--- a/bom/Mazak_VQC_20-40_Retrofit_IO_Workbook.xlsx
+++ b/bom/Mazak_VQC_20-40_Retrofit_IO_Workbook.xlsx
@@ -5554,7 +5554,7 @@
         <x:v>Mesa 7i84U manual pp.2/7-8/47</x:v>
       </x:c>
       <x:c r="K130" s="83" t="str">
-        <x:v>AG verified 08-07-2026: W1 physically RIGHT; direct VIN feed Mean Well +V2 through 5 A branch fuse to TB1-5; return -V4 to TB1-6; 24.0 VDC measured TB1-5 to TB1-6; de-energized continuity 0 ohms. Evidence: docs/commissioning_logs/mazak_commissioning_records_07-08-2026.json</x:v>
+        <x:v>AG verified 08-07-2026: W1 physically RIGHT; direct VIN feed through a 5 A branch fuse to TB1-5; return to TB1-6; 24.0 VDC measured TB1-5 to TB1-6; de-energized continuity 0 ohms. Evidence: docs/commissioning_logs/mazak_commissioning_records_07-08-2026.json</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
